--- a/programs/assembly/sc/tage_test_trace_ibrahim.xlsx
+++ b/programs/assembly/sc/tage_test_trace_ibrahim.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\emerald\zaqal\programs\assembly\sc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE9E9BC9-1833-4B3A-B157-8EDB6DC9267F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{44926EC7-8D6B-4E1D-B56C-897E012C511B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-2895" windowWidth="16440" windowHeight="28440"/>
   </bookViews>
